--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -7489,7 +7489,7 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Published 2026-05-11</t>
+          <t>Published 2026-05-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -7489,7 +7489,7 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Published 2026-05-13</t>
+          <t>Published 2026-05-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2187,12 +2187,12 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Spoke post — definitional; high AEO capture</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-agent-vs-ai-assistant-vs-chatbot/</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -7528,7 +7528,12 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-05-25</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>/blog/ai-agent-vs-ai-assistant-vs-chatbot/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3192,12 +3192,12 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Published (same as K033)</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>/blog/where-do-i-fit-crisis/</t>
+          <t>/blog/ai-adoption-metrics-that-actually-matter/</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -7601,7 +7601,12 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-06-01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>/blog/ai-adoption-metrics-that-actually-matter/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1584,12 +1584,12 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Optimize existing post — add 'build vs buy' H2 and FAQ schema</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/custom-ai-agents-vs-off-shelf-tools-when-to-build/</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Re-target existing post to rank for TCO phrasing</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/hidden-costs-ai-implementation-beyond-technology-budget/</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Optimize FAQ schema, add updated stats, republish</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/why-ai-implementations-fail/</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Add AEO FAQ block; link from pillar</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/90-day-ai-adoption-timeline/</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Already strong — add FAQ schema</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/people-first-ai-strategy/</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Already brand-owned phrase — strengthen with pillar page</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/partnership-not-replacement/</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8287,6 +8287,746 @@
       <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Partnership, Not Replacement</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AI partnership model</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>/blog/partnership-not-replacement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>The \"Where Do I Fit?\" Crisis</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AI employee resistance</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>/blog/where-do-i-fit-crisis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Why AI Implementations Fail</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>why AI implementations fail</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>/blog/why-ai-implementations-fail/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Your First AI Agent: Why Starting Small Is Your Smartest Move</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>first AI agent use case</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>/blog/your-first-ai-agent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>How to Measure ROI on Your First AI Agent</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AI agent ROI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>/blog/measure-roi-first-ai-agent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>'Custom AI Agents vs Off-the-Shelf Tools: When to Build Your Own'</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>build vs buy AI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>/blog/custom-ai-agents-vs-off-shelf-tools-when-to-build/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Why Your AI Strategy Needs a People Strategy First</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>people-first AI strategy</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>/blog/people-first-ai-strategy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>The 90-Day AI Adoption Timeline That Actually Works</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>90 day AI adoption plan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>/blog/90-day-ai-adoption-timeline/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>'The Hidden Costs of AI Implementation: Beyond the Technology Budget'</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AI total cost of ownership</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>/blog/hidden-costs-ai-implementation-beyond-technology-budget/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>The Change Management Playbook for AI Adoption That Actually Works</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AI change management</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>/blog/change-management-playbook-ai-adoption/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Why Your AI Agent Project Stalled (And How to Get Back on Track)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AI agent project recovery</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>/blog/why-ai-agent-project-stalled-how-get-back-on-track/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>'AI Training vs. AI Implementation: Why You Need Both for Success'</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AI training vs implementation</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>/blog/ai-training-vs-implementation-why-you-need-both/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>5 Signs Your Team Is Ready for AI Implementation (And 3 That Mean You Should</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AI implementation readiness signs</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>/blog/signs-team-ready-ai-implementation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>'What Happens After Your AI Agent Goes Live: The Post-Launch Success Framework'</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>post-launch AI agent management</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>/blog/post-launch-ai-agent-management-success-framework/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>When to Hire an AI Consultant vs. Building AI In-House</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AI consultant vs in-house</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>/blog/when-to-hire-ai-consultant-vs-building-in-house/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>How to Scale AI Adoption After Your First Success</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>scaling AI adoption</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>/blog/how-to-scale-ai-adoption-after-first-success/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Why Your Second AI Project Matters More Than Your First</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>second AI project momentum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>/blog/why-your-second-ai-project-matters-more-than-your-first/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Why AI Projects Fail Without Executive Buy-In (And How to Get It)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>executive buy-in for AI</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>/blog/executive-buy-in-ai-projects-leadership-alignment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>How to Train Your Team on AI Without the Overwhelm</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>how to train team on AI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>/blog/how-to-train-team-ai-without-overwhelm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>(backfill)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>'Building Trust in AI: How to Address Team Resistance Before It Starts'</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>building trust in AI</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Backfilled 2026-06-04</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>/blog/building-trust-ai-address-team-resistance/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2120,12 +2120,12 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Spoke post with diagram (SVG); link to pillar</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-agent-architecture-explained-non-engineers/</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -7640,7 +7640,12 @@
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-06-08</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>/blog/ai-agent-architecture-explained-non-engineers/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1249,12 +1249,12 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>New 2,000-word spoke post with downloadable template</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/12-month-ai-transformation-roadmap/</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -7679,7 +7679,12 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-01</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>/blog/12-month-ai-transformation-roadmap/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2589,12 +2589,12 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Spoke with ranges and cost-driver breakdown</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/what-a-custom-ai-agent-costs-and-why/</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -7718,7 +7718,12 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-03</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>/blog/what-a-custom-ai-agent-costs-and-why/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2388,12 +2388,12 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Use-case spoke post</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-agents-for-operations-teams/</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -7757,7 +7757,12 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-06</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>/blog/ai-agents-for-operations-teams/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1316,12 +1316,12 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Spoke post + interactive checklist (use Typeform/Tally)</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-readiness-assessment/</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -7796,7 +7796,12 @@
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-08</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>/blog/ai-readiness-assessment/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3795,12 +3795,12 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Spoke post — low competition, high-value persona</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/guide-to-ai-training-for-executives/</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -7835,7 +7835,12 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-10</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>/blog/guide-to-ai-training-for-executives/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -4532,12 +4532,12 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Spoke with nuanced POV</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/will-ai-replace-my-job/</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -7874,7 +7874,12 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-15</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>/blog/will-ai-replace-my-job/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2254,12 +2254,12 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Spoke post — covers SSO, data handling, audit trails</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/enterprise-ai-agent-security-buyers-checklist/</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -7913,7 +7913,12 @@
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-17</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>/blog/enterprise-ai-agent-security-buyers-checklist/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2455,12 +2455,12 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Use-case spoke post</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-agents-for-finance-teams/</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -7952,7 +7952,12 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-22</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>/blog/ai-agents-for-finance-teams/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1651,12 +1651,12 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Spoke post with scorecard</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/how-to-evaluate-ai-vendors-scorecard/</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -7991,7 +7991,12 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-24</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>/blog/how-to-evaluate-ai-vendors-scorecard/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -4599,12 +4599,12 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Spoke post</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/human-in-the-loop-ai-enterprise/</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
@@ -8030,7 +8030,12 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-27</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>/blog/human-in-the-loop-ai-enterprise/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1455,7 +1455,7 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>/blog/custom-ai-agents-vs-off-shelf-tools-when-to-build/</t>
+          <t>/blog/ai-governance-framework-enterprise/</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -8069,7 +8069,12 @@
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-07-31</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>/blog/ai-governance-framework-enterprise/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1785,12 +1785,12 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Spoke post — uncommon angle, lower competition</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-pilot-to-production-what-goes-wrong/</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -8108,7 +8108,12 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-03</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>/blog/ai-pilot-to-production-what-goes-wrong/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1723,7 +1723,7 @@
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>/blog/hidden-costs-ai-implementation-beyond-technology-budget/</t>
+          <t>/blog/ai-business-case-template/</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -8147,7 +8147,12 @@
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-05</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>/blog/ai-business-case-template/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -4063,12 +4063,12 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Spoke post</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/what-belongs-in-an-ai-literacy-curriculum/</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -8186,7 +8186,12 @@
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-07</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>/blog/what-belongs-in-an-ai-literacy-curriculum/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3996,12 +3996,12 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Spoke post linking to both training solutions</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/how-to-upskill-your-workforce-on-ai/</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -8225,7 +8225,12 @@
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-10</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>/blog/how-to-upskill-your-workforce-on-ai/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3130,7 +3130,7 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>/blog/where-do-i-fit-crisis/</t>
+          <t>/blog/growthmax-ai-adoption-framework/</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -8264,7 +8264,12 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-12</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>/blog/growthmax-ai-adoption-framework/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1517,12 +1517,12 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Spoke post on structure, staffing, charter</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-center-of-excellence-playbook/</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -8303,7 +8303,12 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-14</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>/blog/ai-center-of-excellence-playbook/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3527,12 +3527,12 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Spoke with downloadable template</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/ai-rollout-plan-your-team-will-actually-follow/</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
@@ -8342,7 +8342,12 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-17</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>/blog/ai-rollout-plan-your-team-will-actually-follow/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -4130,12 +4130,12 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Spoke with framework</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/measuring-roi-on-enterprise-ai-training/</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -8381,7 +8381,12 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-08-19</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>/blog/measuring-roi-on-enterprise-ai-training/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3960" yWindow="3120" windowWidth="26720" windowHeight="17040" tabRatio="500" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pillars" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Master Keywords" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AEO Questions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Content Gaps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Calendar (90-day)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tracking Setup" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Quick Wins" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pillars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Keywords" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEO Questions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar (90-day)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracking Setup" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Wins" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Master Keywords'!$A$4:$O$60</definedName>
@@ -28,8 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -174,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -200,6 +201,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7322,7 +7324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9127,6 +9129,652 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>/blog/building-trust-ai-address-team-resistance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>What Makes an AI Agent Enterprise Ready</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>custom AI agents for enterprise</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>What Effective Enterprise AI Training Actually Looks Like</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>enterprise AI training</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>How Enterprise AI Agent Development Actually Works</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>enterprise AI agent development</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>An AI Maturity Model That Skips the Hype</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AI maturity model</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>How to Build an AI Literacy Program That Sticks</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AI literacy program</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Connecting AI Agents to the Systems You Already Run</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>AI agent integration</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Designing Human and AI Collaboration That Holds Up</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>human AI collaboration</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>How Long AI Implementation Really Takes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>AI implementation timeline</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>How to Evaluate an AI Agent Before You Trust It</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>AI agent evaluation</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>46288</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>The AI Skills Your Employees Actually Need</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AI skills for employees</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>How to Prioritize AI Investments When Everything Looks Urgent</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>AI investment prioritization</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Knowing What Your AI Agent Did, and Why</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AI agent observability</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>The AI Adoption KPIs Worth Reporting to Your Board</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AI adoption metrics KPIs</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Responsible AI in the Enterprise, Past the Policy Document</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>responsible AI enterprise</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>What an AI Bootcamp for Engineers Should Cover</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AI bootcamp for engineers</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Where AI Agents Fit in HR Without Replacing the Human Part</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>AI agents for HR</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>(refill 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Spoke</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>When Off-the-Shelf AI Training Is Not Enough</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>custom AI training for companies</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Not started</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3960" yWindow="3120" windowWidth="26720" windowHeight="17040" tabRatio="500" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pillars" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Keywords" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEO Questions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Gaps" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar (90-day)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracking Setup" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Wins" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pillars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Master Keywords" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AEO Questions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Content Gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Calendar (90-day)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tracking Setup" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Quick Wins" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Master Keywords'!$A$4:$O$60</definedName>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Optimize H1 and meta; add enterprise-specific proof section</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/what-makes-an-ai-agent-enterprise-ready/</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -9166,7 +9166,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-09-08</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>/blog/what-makes-an-ai-agent-enterprise-ready/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -3663,12 +3663,12 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Add H2 targeting this; link from new literacy pillar</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/what-effective-enterprise-ai-training-actually-looks-like/</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -9209,7 +9209,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-09-09</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>/blog/what-effective-enterprise-ai-training-actually-looks-like/</t>
         </is>
       </c>
     </row>

--- a/GrowthMax-Keyword-Program.xlsx
+++ b/GrowthMax-Keyword-Program.xlsx
@@ -2055,12 +2055,12 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Add H2 + FAQ schema</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>/blog/how-enterprise-ai-agent-development-actually-works/</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -9252,7 +9252,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Published 2026-09-11</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>/blog/how-enterprise-ai-agent-development-actually-works/</t>
         </is>
       </c>
     </row>
